--- a/artfynd/A 50969-2022 artfynd.xlsx
+++ b/artfynd/A 50969-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50969-2022 artfynd.xlsx
+++ b/artfynd/A 50969-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6932857</v>
+        <v>6932856</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754588.9268400507</v>
+        <v>754558</v>
       </c>
       <c r="R2" t="n">
-        <v>7084814.2012485</v>
+        <v>7084865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6993798</v>
+        <v>6993797</v>
       </c>
       <c r="B3" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754657.6021029101</v>
+        <v>754626</v>
       </c>
       <c r="R3" t="n">
-        <v>7084833.092872533</v>
+        <v>7084870</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +845,11 @@
           <t>2013-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-10-13</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,16 +862,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>låga # tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6993801</v>
+        <v>6993798</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754658.92725528</v>
+        <v>754658</v>
       </c>
       <c r="R4" t="n">
-        <v>7084816.780550133</v>
+        <v>7084833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,21 +947,11 @@
           <t>2013-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,6 +964,16 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>låga # tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54902998</v>
+        <v>54902995</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754752.7764376579</v>
+        <v>754768</v>
       </c>
       <c r="R5" t="n">
-        <v>7084843.044856815</v>
+        <v>7084910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,19 +1059,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,15 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54902997</v>
+        <v>54902996</v>
       </c>
       <c r="B6" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754741.975689566</v>
+        <v>754763</v>
       </c>
       <c r="R6" t="n">
-        <v>7084882.9948876</v>
+        <v>7084904</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,19 +1156,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55076703</v>
+        <v>54902997</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754568.6432650315</v>
+        <v>754742</v>
       </c>
       <c r="R7" t="n">
-        <v>7084839.624624161</v>
+        <v>7084883</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,22 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-09-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-09-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74682590</v>
+        <v>54902998</v>
       </c>
       <c r="B8" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,34 +1293,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+          <t>Röbäcksskogen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754594.808505739</v>
+        <v>754753</v>
       </c>
       <c r="R8" t="n">
-        <v>7084829.323727285</v>
+        <v>7084843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,22 +1347,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-11-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-11-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,11 +1363,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tallstubbe</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1489,58 +1379,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103262267</v>
+        <v>54902994</v>
       </c>
       <c r="B9" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Röbäck, Vb</t>
+          <t>Röbäcksskogen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754656.2161949852</v>
+        <v>754764</v>
       </c>
       <c r="R9" t="n">
-        <v>7084872.032853391</v>
+        <v>7084917</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,22 +1444,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,15 +1464,821 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>60963561</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>754694</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7084794</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-08-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-08-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>55076703</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>754569</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7084840</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-09-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-09-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6932857</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>754589</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7084814</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-09-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-09-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6932858</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>754624</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7084776</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2013-09-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2013-09-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6993801</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>754659</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7084817</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103262267</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>754656</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7084872</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Lars Karlsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Lars Karlsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>68474139</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>754696</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7084901</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-11-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-11-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74682590</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>754595</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7084829</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-11-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-11-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50969-2022 artfynd.xlsx
+++ b/artfynd/A 50969-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6932856</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993797</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993798</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902995</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902996</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902997</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902994</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60963561</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55076703</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6932857</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6932858</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993801</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262267</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2177,6 +2252,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68474139</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2279,8 +2359,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74682590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>